--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_List/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_List/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfccc892ce180406c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R01583611572b4da4"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_List/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_List/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R01583611572b4da4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R492dc953967e4ddb"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_List/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_List/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R492dc953967e4ddb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6cf772453f224c17"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_List/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_List/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6cf772453f224c17"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R72b90b0f39ca4c8b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_List/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_List/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R72b90b0f39ca4c8b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R608df9089fa44694"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_List/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_List/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R608df9089fa44694"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5920885fbee14a22"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_List/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_List/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5920885fbee14a22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R66b2e5e0634040f2"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_List/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_List/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R66b2e5e0634040f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R321d58c3a9d64e65"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_List/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_List/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R321d58c3a9d64e65"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1d654d2f44414716"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_List/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_List/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1d654d2f44414716"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7daa57f9a07e4bc5"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_List/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_List/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7daa57f9a07e4bc5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2ac7d7cc2a7c46ae"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_List/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_List/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2ac7d7cc2a7c46ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7fe09e69b0c94260"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_List/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_List/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7fe09e69b0c94260"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8c54141da1f54ba2"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_List/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_List/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8c54141da1f54ba2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Reaafdb8407c943f8"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_List/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_List/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Reaafdb8407c943f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R180f793c30144f11"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_List/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_List/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R180f793c30144f11"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9d7a72c8898f42d6"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_List/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_List/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9d7a72c8898f42d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R52ac6588ae9548b9"/>
   </x:sheets>
 </x:workbook>
 </file>
